--- a/outputs/evaluacion_tfidf.xlsx
+++ b/outputs/evaluacion_tfidf.xlsx
@@ -470,19 +470,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.0907386</v>
+        <v>0.094836</v>
       </c>
       <c r="D2" t="n">
-        <v>0.14318</v>
+        <v>0.147837</v>
       </c>
       <c r="E2" t="n">
-        <v>0.07074900000000001</v>
+        <v>0.070767</v>
       </c>
       <c r="F2" t="n">
         <v>2</v>
       </c>
       <c r="G2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H2" t="n">
         <v>10</v>
@@ -500,10 +500,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.1010626</v>
+        <v>0.1030222</v>
       </c>
       <c r="D3" t="n">
-        <v>0.228107</v>
+        <v>0.230606</v>
       </c>
       <c r="E3" t="n">
         <v>0.06666999999999999</v>
@@ -512,7 +512,7 @@
         <v>2</v>
       </c>
       <c r="G3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H3" t="n">
         <v>10</v>
@@ -530,13 +530,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.07875989999999999</v>
+        <v>0.0820563</v>
       </c>
       <c r="D4" t="n">
         <v>0.113544</v>
       </c>
       <c r="E4" t="n">
-        <v>0.066608</v>
+        <v>0.06843200000000001</v>
       </c>
       <c r="F4" t="n">
         <v>2</v>
@@ -560,13 +560,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.06691240000000001</v>
+        <v>0.06764390000000001</v>
       </c>
       <c r="D5" t="n">
-        <v>0.09193999999999999</v>
+        <v>0.09194099999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>0.058872</v>
+        <v>0.058869</v>
       </c>
       <c r="F5" t="n">
         <v>2</v>
@@ -590,10 +590,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.1153229</v>
+        <v>0.1167757</v>
       </c>
       <c r="D6" t="n">
-        <v>0.282578</v>
+        <v>0.282572</v>
       </c>
       <c r="E6" t="n">
         <v>0.058063</v>
@@ -620,19 +620,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.0945474</v>
+        <v>0.0931965</v>
       </c>
       <c r="D7" t="n">
-        <v>0.189507</v>
+        <v>0.189503</v>
       </c>
       <c r="E7" t="n">
-        <v>0.067055</v>
+        <v>0.06475400000000001</v>
       </c>
       <c r="F7" t="n">
         <v>2</v>
       </c>
       <c r="G7" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H7" t="n">
         <v>10</v>
@@ -650,13 +650,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.1080635</v>
+        <v>0.110303</v>
       </c>
       <c r="D8" t="n">
-        <v>0.145535</v>
+        <v>0.163419</v>
       </c>
       <c r="E8" t="n">
-        <v>0.083527</v>
+        <v>0.083402</v>
       </c>
       <c r="F8" t="n">
         <v>2</v>
@@ -680,10 +680,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.0529767</v>
+        <v>0.05394060000000001</v>
       </c>
       <c r="D9" t="n">
-        <v>0.07148400000000001</v>
+        <v>0.071424</v>
       </c>
       <c r="E9" t="n">
         <v>0.045182</v>
